--- a/data/NDX.xlsx
+++ b/data/NDX.xlsx
@@ -36620,6 +36620,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1577">
+      <c r="A1577" s="1" t="n">
+        <v>46275.5625</v>
+      </c>
+      <c r="B1577" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1577" t="n">
+        <v>29103.509765625</v>
+      </c>
+      <c r="D1577" t="n">
+        <v>29103.509765625</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>29103.509765625</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>29103.509765625</v>
+      </c>
+      <c r="G1577" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="1" t="n">
+        <v>46276.5625</v>
+      </c>
+      <c r="B1578" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1578" t="n">
+        <v>29368.439453125</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>29368.439453125</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>29368.439453125</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>29368.439453125</v>
+      </c>
+      <c r="G1578" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NDX.xlsx
+++ b/data/NDX.xlsx
@@ -36666,6 +36666,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1579">
+      <c r="A1579" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1579" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1579" t="n">
+        <v>29127.16015625</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>29127.16015625</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>29127.16015625</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>29127.16015625</v>
+      </c>
+      <c r="G1579" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NDX.xlsx
+++ b/data/NDX.xlsx
@@ -36689,6 +36689,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1580">
+      <c r="A1580" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1580" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1580" t="n">
+        <v>28937.83984375</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>28937.83984375</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>28937.83984375</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>28937.83984375</v>
+      </c>
+      <c r="G1580" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NDX.xlsx
+++ b/data/NDX.xlsx
@@ -36712,6 +36712,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1581">
+      <c r="A1581" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1581" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1581" t="n">
+        <v>28945.060546875</v>
+      </c>
+      <c r="D1581" t="n">
+        <v>28945.060546875</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>28945.060546875</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>28945.060546875</v>
+      </c>
+      <c r="G1581" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
